--- a/forms/dist/obs_household_visit.xlsx
+++ b/forms/dist/obs_household_visit.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -460,6 +460,8 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,6 +538,16 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>parameters</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>choice_filter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>save_to</t>
         </is>
       </c>
     </row>
@@ -563,6 +575,8 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -588,6 +602,8 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -613,6 +629,8 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -638,6 +656,8 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -663,6 +683,8 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -700,6 +722,8 @@
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -733,6 +757,8 @@
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -774,6 +800,8 @@
       </c>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -815,6 +843,8 @@
       </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -840,6 +870,8 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -869,6 +901,8 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -898,6 +932,8 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -935,6 +971,8 @@
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -976,6 +1014,8 @@
       </c>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1029,6 +1069,8 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1090,6 +1132,8 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1115,6 +1159,8 @@
       <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1144,6 +1190,8 @@
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1181,6 +1229,8 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1218,6 +1268,8 @@
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1259,6 +1311,8 @@
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1316,6 +1370,8 @@
       </c>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1369,6 +1425,8 @@
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1426,6 +1484,8 @@
       </c>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1479,6 +1539,8 @@
       </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1532,6 +1594,8 @@
       </c>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1585,6 +1649,8 @@
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1638,6 +1704,8 @@
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1691,6 +1759,8 @@
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1744,6 +1814,8 @@
       </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1769,6 +1841,8 @@
       <c r="M32" s="3" t="inlineStr"/>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1810,6 +1884,8 @@
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1867,6 +1943,8 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1904,6 +1982,8 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1941,6 +2021,8 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1966,6 +2048,8 @@
       <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2007,6 +2091,8 @@
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2056,6 +2142,8 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2097,6 +2185,8 @@
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2138,6 +2228,8 @@
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2179,6 +2271,8 @@
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2220,6 +2314,8 @@
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2245,6 +2341,8 @@
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2282,6 +2380,8 @@
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2331,6 +2431,8 @@
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2380,6 +2482,8 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2405,6 +2509,8 @@
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="3" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2450,6 +2556,8 @@
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
